--- a/san-pham.xlsx
+++ b/san-pham.xlsx
@@ -252,9 +252,6 @@
     <t>Barcode</t>
   </si>
   <si>
-    <t>0001</t>
-  </si>
-  <si>
     <t>0002</t>
   </si>
   <si>
@@ -631,6 +628,9 @@
   </si>
   <si>
     <t>0109</t>
+  </si>
+  <si>
+    <t>00013</t>
   </si>
 </sst>
 </file>
@@ -1020,7 +1020,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
@@ -1072,7 +1072,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>11</v>
@@ -1098,7 +1098,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>14</v>
@@ -1124,7 +1124,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>18</v>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>57</v>
@@ -1176,7 +1176,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>56</v>
@@ -1202,7 +1202,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>24</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>24</v>
@@ -1254,7 +1254,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -1280,7 +1280,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>27</v>
@@ -1306,7 +1306,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>27</v>
@@ -1332,7 +1332,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>30</v>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>33</v>
@@ -1384,7 +1384,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>33</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>33</v>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>36</v>
@@ -1462,7 +1462,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>40</v>
@@ -1488,7 +1488,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>58</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>42</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>43</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>44</v>
@@ -1592,7 +1592,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>44</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>46</v>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>46</v>
@@ -1670,7 +1670,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>47</v>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>50</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>51</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>52</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>53</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>59</v>
@@ -1826,7 +1826,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>62</v>
@@ -1852,7 +1852,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>63</v>
@@ -1878,7 +1878,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>65</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>64</v>
@@ -1930,7 +1930,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>64</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>66</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>66</v>
@@ -2008,7 +2008,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>66</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>66</v>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>66</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
         <v>67</v>
@@ -2112,7 +2112,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
         <v>67</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B45" t="s">
         <v>67</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
         <v>67</v>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B47" t="s">
         <v>70</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>70</v>
@@ -2242,7 +2242,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>70</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B50" t="s">
         <v>70</v>
@@ -2294,7 +2294,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>75</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>75</v>
@@ -2346,7 +2346,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>75</v>
@@ -2372,7 +2372,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>75</v>
@@ -2398,7 +2398,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>73</v>
@@ -2424,7 +2424,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>73</v>
@@ -2450,10 +2450,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B57" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C57" t="s">
         <v>37</v>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C58" t="s">
         <v>37</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B59" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C59" t="s">
         <v>37</v>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B60" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C60" t="s">
         <v>37</v>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C61" t="s">
         <v>37</v>
@@ -2580,10 +2580,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C62" t="s">
         <v>37</v>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" t="s">
         <v>37</v>
@@ -2618,7 +2618,7 @@
         <v>31</v>
       </c>
       <c r="E63" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F63">
         <v>450000</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B64" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C64" t="s">
         <v>37</v>
@@ -2658,10 +2658,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C65" t="s">
         <v>37</v>
@@ -2684,10 +2684,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C66" t="s">
         <v>37</v>
@@ -2696,7 +2696,7 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F66">
         <v>450000</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C67" t="s">
         <v>37</v>
@@ -2722,7 +2722,7 @@
         <v>10</v>
       </c>
       <c r="E67" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F67">
         <v>450000</v>
@@ -2736,10 +2736,10 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C68" t="s">
         <v>37</v>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C69" t="s">
         <v>37</v>
@@ -2788,10 +2788,10 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C70" t="s">
         <v>37</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C71" t="s">
         <v>37</v>
@@ -2826,7 +2826,7 @@
         <v>31</v>
       </c>
       <c r="E71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F71">
         <v>440000</v>
@@ -2840,10 +2840,10 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B72" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C72" t="s">
         <v>37</v>
@@ -2866,10 +2866,10 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B73" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C73" t="s">
         <v>37</v>
@@ -2892,10 +2892,10 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B74" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C74" t="s">
         <v>37</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B75" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C75" t="s">
         <v>37</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B76" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C76" t="s">
         <v>37</v>
@@ -2970,10 +2970,10 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B77" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C77" t="s">
         <v>37</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C78" t="s">
         <v>37</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C79" t="s">
         <v>37</v>
@@ -3048,10 +3048,10 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B80" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C80" t="s">
         <v>37</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B81" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C81" t="s">
         <v>37</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B82" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C82" t="s">
         <v>37</v>
@@ -3112,7 +3112,7 @@
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F82">
         <v>450000</v>
@@ -3126,10 +3126,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B83" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C83" t="s">
         <v>37</v>
@@ -3138,7 +3138,7 @@
         <v>10</v>
       </c>
       <c r="E83" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F83">
         <v>450000</v>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B84" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C84" t="s">
         <v>37</v>
@@ -3178,10 +3178,10 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C85" t="s">
         <v>37</v>
@@ -3204,10 +3204,10 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B86" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C86" t="s">
         <v>37</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B87" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C87" t="s">
         <v>37</v>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B88" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C88" t="s">
         <v>37</v>
@@ -3282,10 +3282,10 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B89" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C89" t="s">
         <v>37</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B90" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C90" t="s">
         <v>26</v>
@@ -3334,10 +3334,10 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B91" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C91" t="s">
         <v>37</v>
@@ -3346,7 +3346,7 @@
         <v>10</v>
       </c>
       <c r="E91" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F91">
         <v>450000</v>
@@ -3360,10 +3360,10 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B92" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C92" t="s">
         <v>37</v>
@@ -3372,7 +3372,7 @@
         <v>10</v>
       </c>
       <c r="E92" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F92">
         <v>450000</v>
@@ -3386,10 +3386,10 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B93" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C93" t="s">
         <v>37</v>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B94" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C94" t="s">
         <v>37</v>
@@ -3438,10 +3438,10 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B95" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C95" t="s">
         <v>37</v>
@@ -3464,10 +3464,10 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B96" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C96" t="s">
         <v>37</v>
@@ -3490,10 +3490,10 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B97" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C97" t="s">
         <v>37</v>
@@ -3516,10 +3516,10 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B98" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C98" t="s">
         <v>37</v>
@@ -3542,10 +3542,10 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B99" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C99" t="s">
         <v>37</v>
@@ -3554,7 +3554,7 @@
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F99">
         <v>330000</v>
@@ -3568,10 +3568,10 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B100" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C100" t="s">
         <v>37</v>
@@ -3580,7 +3580,7 @@
         <v>10</v>
       </c>
       <c r="E100" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F100">
         <v>330000</v>
@@ -3594,10 +3594,10 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B101" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C101" t="s">
         <v>37</v>
@@ -3606,7 +3606,7 @@
         <v>10</v>
       </c>
       <c r="E101" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F101">
         <v>330000</v>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B102" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C102" t="s">
         <v>37</v>
@@ -3646,10 +3646,10 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B103" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C103" t="s">
         <v>37</v>
@@ -3672,10 +3672,10 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B104" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C104" t="s">
         <v>37</v>
@@ -3698,10 +3698,10 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B105" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C105" t="s">
         <v>37</v>
@@ -3724,10 +3724,10 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B106" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C106" t="s">
         <v>37</v>
@@ -3736,7 +3736,7 @@
         <v>31</v>
       </c>
       <c r="E106" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F106">
         <v>400000</v>
@@ -3750,10 +3750,10 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B107" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C107" t="s">
         <v>37</v>
@@ -3762,7 +3762,7 @@
         <v>31</v>
       </c>
       <c r="E107" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F107">
         <v>400000</v>
@@ -3776,10 +3776,10 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B108" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C108" t="s">
         <v>37</v>
@@ -3788,7 +3788,7 @@
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F108">
         <v>400000</v>
@@ -3802,10 +3802,10 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B109" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C109" t="s">
         <v>37</v>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B110" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C110" t="s">
         <v>37</v>
